--- a/outputs/card_inventory_2026-07-25/topdeck_to_worlds_mechanically_implemented_cards.xlsx
+++ b/outputs/card_inventory_2026-07-25/topdeck_to_worlds_mechanically_implemented_cards.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2918fb7e94574e5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="2" r:id="R899feee51add4f08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Tokens" sheetId="3" r:id="Re0710e65a49c4ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5c2d664b55034c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="2" r:id="Rcfa830b3fa1c4a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Tokens" sheetId="3" r:id="R053c004d9c354812"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -538,7 +538,7 @@
   <x:sheetData>
     <x:row r="1" ht="31.5" customHeight="1">
       <x:c r="A1" s="35" t="str">
-        <x:v>Topdeck to Worlds — Mechanically Implemented Card Catalog</x:v>
+        <x:v>TOP CUT: Locals to Worlds — Mechanically Implemented Card Catalog</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -6598,7 +6598,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d6f72705ce3451f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ec663de43a84e6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6700,7 +6700,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re567ed291a3b40f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd78ff7c4ab0e4769"/>
   </x:tableParts>
 </x:worksheet>
 </file>